--- a/Data-Analytics/docs/FLEX DRIVE - Permítenos Conocerte.xlsx
+++ b/Data-Analytics/docs/FLEX DRIVE - Permítenos Conocerte.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leshi\OneDrive\Escritorio\University\006- Ninth Semester\000- Flex Drive\Flex-Drive\Data-Analytics\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\7SEMESTRE\FlexDrive\big data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC9A6E2-7D7C-4AF7-AC7C-1E6128C938B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE7762F7-991D-4111-844D-87249F76B51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4777,96 +4777,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CI384"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="104" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="90.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="90.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="137.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="137.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="73.109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="70" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="125.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="67.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="59.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="125.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="67.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="240.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="72.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="217.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="223.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="96.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="240.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="72.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="217.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="223.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="96.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="255.6640625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="44" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="113" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="39.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="39.44140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="50.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="49.88671875" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="51" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="37.85546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="240.28515625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="132.42578125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="116.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="47.5703125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="44.28515625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="55.7109375" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="129.28515625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="155.28515625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="240.33203125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="132.44140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="116.6640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="47.5546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="129.33203125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="155.33203125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="43" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="73.85546875" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="73.88671875" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="47.44140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="39.5546875" bestFit="1" customWidth="1"/>
     <col min="69" max="69" width="46" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="47.5703125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="132.42578125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="128.7109375" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="47.5703125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="39.140625" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="47.5703125" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="52.85546875" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="47.5546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="132.44140625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="128.6640625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="47.5546875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="39.109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="47.5546875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="57.88671875" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="52.88671875" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="86" max="86" width="74" bestFit="1" customWidth="1"/>
     <col min="87" max="87" width="161" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="2" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>4</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>6</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>7</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>8</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>9</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>11</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>12</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>13</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>14</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>15</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>17</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>18</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>19</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="18" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>20</v>
       </c>
@@ -7422,7 +7422,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>21</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>22</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>23</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>24</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>27</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>28</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>29</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>30</v>
       </c>
@@ -8984,7 +8984,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="29" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>31</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="30" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>32</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>33</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>34</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>35</v>
       </c>
@@ -9900,7 +9900,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>36</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="35" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>37</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>38</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>39</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>40</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="39" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>41</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="40" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>42</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="41" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>43</v>
       </c>
@@ -11343,7 +11343,7 @@
       <c r="CH41" s="1"/>
       <c r="CI41" s="1"/>
     </row>
-    <row r="42" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>44</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>45</v>
       </c>
@@ -11713,7 +11713,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="44" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>46</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>47</v>
       </c>
@@ -12125,7 +12125,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="46" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>48</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="47" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>49</v>
       </c>
@@ -12494,7 +12494,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="48" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>50</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="49" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>51</v>
       </c>
@@ -12864,7 +12864,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="50" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>52</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="51" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>53</v>
       </c>
@@ -13276,7 +13276,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="52" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>54</v>
       </c>
@@ -13471,7 +13471,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="53" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>55</v>
       </c>
@@ -13666,7 +13666,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="54" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>56</v>
       </c>
@@ -13899,7 +13899,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="55" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>57</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>58</v>
       </c>
@@ -14229,7 +14229,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="57" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>59</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="58" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>60</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="59" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>61</v>
       </c>
@@ -14860,7 +14860,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="60" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>62</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="61" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>63</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="62" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>64</v>
       </c>
@@ -15439,7 +15439,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="63" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>65</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="64" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>66</v>
       </c>
@@ -15825,7 +15825,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="65" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>67</v>
       </c>
@@ -15964,7 +15964,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="66" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>68</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="67" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>69</v>
       </c>
@@ -16348,7 +16348,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="68" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>70</v>
       </c>
@@ -16493,7 +16493,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="69" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>71</v>
       </c>
@@ -16678,7 +16678,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="70" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>72</v>
       </c>
@@ -16919,7 +16919,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>73</v>
       </c>
@@ -17162,7 +17162,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>74</v>
       </c>
@@ -17309,7 +17309,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="73" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>75</v>
       </c>
@@ -17462,7 +17462,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="74" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>76</v>
       </c>
@@ -17703,7 +17703,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="75" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>77</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="76" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>78</v>
       </c>
@@ -18175,7 +18175,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="77" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>79</v>
       </c>
@@ -18318,7 +18318,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="78" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>80</v>
       </c>
@@ -18517,7 +18517,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="79" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>81</v>
       </c>
@@ -18662,7 +18662,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="80" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>82</v>
       </c>
@@ -18901,7 +18901,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="81" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>83</v>
       </c>
@@ -19140,7 +19140,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="82" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>84</v>
       </c>
@@ -19373,7 +19373,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="83" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>85</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="84" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>86</v>
       </c>
@@ -19741,7 +19741,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="85" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>87</v>
       </c>
@@ -19934,7 +19934,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="86" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>88</v>
       </c>
@@ -20073,7 +20073,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="87" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>89</v>
       </c>
@@ -20208,7 +20208,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="88" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>90</v>
       </c>
@@ -20461,7 +20461,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="89" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>91</v>
       </c>
@@ -20596,7 +20596,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="90" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>92</v>
       </c>
@@ -20735,7 +20735,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="91" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>93</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="92" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>94</v>
       </c>
@@ -21061,7 +21061,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="93" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>95</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="94" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>96</v>
       </c>
@@ -21345,7 +21345,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="95" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>97</v>
       </c>
@@ -21484,7 +21484,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="96" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>98</v>
       </c>
@@ -21623,7 +21623,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="97" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>99</v>
       </c>
@@ -21852,7 +21852,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="98" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>100</v>
       </c>
@@ -21991,7 +21991,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="99" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>101</v>
       </c>
@@ -22170,7 +22170,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="100" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>102</v>
       </c>
@@ -22355,7 +22355,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="101" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>103</v>
       </c>
@@ -22534,7 +22534,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="102" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>104</v>
       </c>
@@ -22713,7 +22713,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="103" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>105</v>
       </c>
@@ -22898,7 +22898,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="104" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>106</v>
       </c>
@@ -23037,7 +23037,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="105" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>107</v>
       </c>
@@ -23182,7 +23182,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="106" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>108</v>
       </c>
@@ -23419,7 +23419,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="107" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>109</v>
       </c>
@@ -23656,7 +23656,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="108" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>110</v>
       </c>
@@ -23885,7 +23885,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="109" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>111</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="110" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>112</v>
       </c>
@@ -24207,7 +24207,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="111" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>113</v>
       </c>
@@ -24354,7 +24354,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="112" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>114</v>
       </c>
@@ -24493,7 +24493,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="113" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>115</v>
       </c>
@@ -24632,7 +24632,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="114" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>116</v>
       </c>
@@ -24771,7 +24771,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>117</v>
       </c>
@@ -24918,7 +24918,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="116" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>118</v>
       </c>
@@ -25067,7 +25067,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="117" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>119</v>
       </c>
@@ -25258,7 +25258,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="118" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>120</v>
       </c>
@@ -25445,7 +25445,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="119" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>121</v>
       </c>
@@ -25682,7 +25682,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="120" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>122</v>
       </c>
@@ -25873,7 +25873,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="121" spans="1:87" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:87" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>123</v>
       </c>
@@ -26104,7 +26104,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="122" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>124</v>
       </c>
@@ -26335,7 +26335,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="123" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>125</v>
       </c>
@@ -26570,7 +26570,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="124" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>126</v>
       </c>
@@ -26801,7 +26801,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="125" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>127</v>
       </c>
@@ -27032,7 +27032,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="126" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>128</v>
       </c>
@@ -27269,7 +27269,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="127" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>129</v>
       </c>
@@ -27416,7 +27416,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="128" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>130</v>
       </c>
@@ -27599,7 +27599,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="129" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>131</v>
       </c>
@@ -27782,7 +27782,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="130" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>132</v>
       </c>
@@ -28019,7 +28019,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="131" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>133</v>
       </c>
@@ -28202,7 +28202,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="132" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>134</v>
       </c>
@@ -28349,7 +28349,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="133" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>135</v>
       </c>
@@ -28486,7 +28486,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="134" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>136</v>
       </c>
@@ -28725,7 +28725,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="135" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>137</v>
       </c>
@@ -28908,7 +28908,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="136" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>138</v>
       </c>
@@ -29137,7 +29137,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>139</v>
       </c>
@@ -29276,7 +29276,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="138" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>140</v>
       </c>
@@ -29413,7 +29413,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="139" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>141</v>
       </c>
@@ -29550,7 +29550,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="140" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>142</v>
       </c>
@@ -29685,7 +29685,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="141" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>143</v>
       </c>
@@ -29820,7 +29820,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="142" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>144</v>
       </c>
@@ -29959,7 +29959,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="143" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>145</v>
       </c>
@@ -30188,7 +30188,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="144" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>146</v>
       </c>
@@ -30327,7 +30327,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="145" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>147</v>
       </c>
@@ -30556,7 +30556,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="146" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>148</v>
       </c>
@@ -30739,7 +30739,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="147" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>149</v>
       </c>
@@ -30922,7 +30922,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="148" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>150</v>
       </c>
@@ -31061,7 +31061,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="149" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>151</v>
       </c>
@@ -31208,7 +31208,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="150" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>152</v>
       </c>
@@ -31449,7 +31449,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="151" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>153</v>
       </c>
@@ -31688,7 +31688,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="152" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>154</v>
       </c>
@@ -31917,7 +31917,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="153" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>155</v>
       </c>
@@ -32056,7 +32056,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="154" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>156</v>
       </c>
@@ -32203,7 +32203,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="155" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>157</v>
       </c>
@@ -32438,7 +32438,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="156" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>158</v>
       </c>
@@ -32577,7 +32577,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>159</v>
       </c>
@@ -32806,7 +32806,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="158" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>160</v>
       </c>
@@ -33035,7 +33035,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="159" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>161</v>
       </c>
@@ -33272,7 +33272,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="160" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>162</v>
       </c>
@@ -33419,7 +33419,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="161" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>163</v>
       </c>
@@ -33566,7 +33566,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="162" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>164</v>
       </c>
@@ -33799,7 +33799,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="163" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>165</v>
       </c>
@@ -33984,7 +33984,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="164" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>166</v>
       </c>
@@ -34167,7 +34167,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="165" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>167</v>
       </c>
@@ -34306,7 +34306,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="166" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>168</v>
       </c>
@@ -34445,7 +34445,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="167" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>169</v>
       </c>
@@ -34672,7 +34672,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="168" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>170</v>
       </c>
@@ -34875,7 +34875,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="169" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>171</v>
       </c>
@@ -35070,7 +35070,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="170" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>172</v>
       </c>
@@ -35165,7 +35165,7 @@
       <c r="CH170" s="1"/>
       <c r="CI170" s="1"/>
     </row>
-    <row r="171" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>173</v>
       </c>
@@ -35408,7 +35408,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="172" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>174</v>
       </c>
@@ -35547,7 +35547,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="173" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>175</v>
       </c>
@@ -35686,7 +35686,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="174" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>176</v>
       </c>
@@ -35917,7 +35917,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="175" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>177</v>
       </c>
@@ -36146,7 +36146,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="176" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>178</v>
       </c>
@@ -36283,7 +36283,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="177" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>179</v>
       </c>
@@ -36430,7 +36430,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="178" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>180</v>
       </c>
@@ -36665,7 +36665,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="179" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>181</v>
       </c>
@@ -36804,7 +36804,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="180" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>182</v>
       </c>
@@ -36951,7 +36951,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="181" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>183</v>
       </c>
@@ -37094,7 +37094,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="182" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>184</v>
       </c>
@@ -37233,7 +37233,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="183" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>185</v>
       </c>
@@ -37372,7 +37372,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="184" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>186</v>
       </c>
@@ -37551,7 +37551,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="185" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>187</v>
       </c>
@@ -37736,7 +37736,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="186" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>188</v>
       </c>
@@ -37965,7 +37965,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="187" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>189</v>
       </c>
@@ -38150,7 +38150,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="188" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>190</v>
       </c>
@@ -38377,7 +38377,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="189" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>191</v>
       </c>
@@ -38516,7 +38516,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="190" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>192</v>
       </c>
@@ -38745,7 +38745,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="191" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>193</v>
       </c>
@@ -38884,7 +38884,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="192" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>194</v>
       </c>
@@ -39031,7 +39031,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="193" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>195</v>
       </c>
@@ -39214,7 +39214,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="194" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>196</v>
       </c>
@@ -39353,7 +39353,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="195" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>197</v>
       </c>
@@ -39536,7 +39536,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="196" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>198</v>
       </c>
@@ -39785,7 +39785,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="197" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>199</v>
       </c>
@@ -40016,7 +40016,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="198" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>200</v>
       </c>
@@ -40245,7 +40245,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="199" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>201</v>
       </c>
@@ -40430,7 +40430,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="200" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>202</v>
       </c>
@@ -40569,7 +40569,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="201" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>203</v>
       </c>
@@ -40822,7 +40822,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="202" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>204</v>
       </c>
@@ -41017,7 +41017,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="203" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>205</v>
       </c>
@@ -41198,7 +41198,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="204" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>206</v>
       </c>
@@ -41389,7 +41389,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="205" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>207</v>
       </c>
@@ -41626,7 +41626,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="206" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>208</v>
       </c>
@@ -41855,7 +41855,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="207" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>209</v>
       </c>
@@ -42008,7 +42008,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="208" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>210</v>
       </c>
@@ -42161,7 +42161,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="209" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>211</v>
       </c>
@@ -42372,7 +42372,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="210" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>212</v>
       </c>
@@ -42555,7 +42555,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="211" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>213</v>
       </c>
@@ -42740,7 +42740,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="212" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>214</v>
       </c>
@@ -42969,7 +42969,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="213" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>215</v>
       </c>
@@ -43158,7 +43158,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="214" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>216</v>
       </c>
@@ -43297,7 +43297,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="215" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>217</v>
       </c>
@@ -43478,7 +43478,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="216" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>218</v>
       </c>
@@ -43707,7 +43707,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="217" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>219</v>
       </c>
@@ -43856,7 +43856,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="218" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>220</v>
       </c>
@@ -43999,7 +43999,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="219" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>221</v>
       </c>
@@ -44182,7 +44182,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="220" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>222</v>
       </c>
@@ -44367,7 +44367,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="221" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>223</v>
       </c>
@@ -44510,7 +44510,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="222" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>224</v>
       </c>
@@ -44605,7 +44605,7 @@
       <c r="CH222" s="1"/>
       <c r="CI222" s="1"/>
     </row>
-    <row r="223" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>225</v>
       </c>
@@ -44788,7 +44788,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="224" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>226</v>
       </c>
@@ -45037,7 +45037,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="225" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>227</v>
       </c>
@@ -45280,7 +45280,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="226" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>228</v>
       </c>
@@ -45469,7 +45469,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="227" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>229</v>
       </c>
@@ -45608,7 +45608,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="228" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>230</v>
       </c>
@@ -45791,7 +45791,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="229" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>231</v>
       </c>
@@ -45978,7 +45978,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="230" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>232</v>
       </c>
@@ -46117,7 +46117,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="231" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>233</v>
       </c>
@@ -46300,7 +46300,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="232" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>234</v>
       </c>
@@ -46453,7 +46453,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="233" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>235</v>
       </c>
@@ -46636,7 +46636,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="234" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>236</v>
       </c>
@@ -46875,7 +46875,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="235" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>237</v>
       </c>
@@ -47036,7 +47036,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="236" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>238</v>
       </c>
@@ -47265,7 +47265,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="237" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>239</v>
       </c>
@@ -47404,7 +47404,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="238" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>240</v>
       </c>
@@ -47641,7 +47641,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="239" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>241</v>
       </c>
@@ -47878,7 +47878,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="240" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>242</v>
       </c>
@@ -48125,7 +48125,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="241" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>243</v>
       </c>
@@ -48362,7 +48362,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="242" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>244</v>
       </c>
@@ -48591,7 +48591,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="243" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>245</v>
       </c>
@@ -48730,7 +48730,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="244" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>246</v>
       </c>
@@ -48965,7 +48965,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="245" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>247</v>
       </c>
@@ -49112,7 +49112,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="246" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>248</v>
       </c>
@@ -49347,7 +49347,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="247" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>249</v>
       </c>
@@ -49592,7 +49592,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="248" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>250</v>
       </c>
@@ -49731,7 +49731,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="249" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>251</v>
       </c>
@@ -49980,7 +49980,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="250" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>252</v>
       </c>
@@ -50221,7 +50221,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="251" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>253</v>
       </c>
@@ -50374,7 +50374,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="252" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>254</v>
       </c>
@@ -50521,7 +50521,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="253" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>255</v>
       </c>
@@ -50750,7 +50750,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="254" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>256</v>
       </c>
@@ -50979,7 +50979,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="255" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>257</v>
       </c>
@@ -51126,7 +51126,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="256" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>258</v>
       </c>
@@ -51265,7 +51265,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="257" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>259</v>
       </c>
@@ -51410,7 +51410,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="258" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>260</v>
       </c>
@@ -51549,7 +51549,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="259" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>261</v>
       </c>
@@ -51738,7 +51738,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="260" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>262</v>
       </c>
@@ -51979,7 +51979,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="261" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>263</v>
       </c>
@@ -52208,7 +52208,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="262" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>264</v>
       </c>
@@ -52419,7 +52419,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="263" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>265</v>
       </c>
@@ -52558,7 +52558,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="264" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>266</v>
       </c>
@@ -52701,7 +52701,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="265" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>267</v>
       </c>
@@ -52930,7 +52930,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="266" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>268</v>
       </c>
@@ -53171,7 +53171,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="267" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>269</v>
       </c>
@@ -53358,7 +53358,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="268" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>270</v>
       </c>
@@ -53585,7 +53585,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="269" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>271</v>
       </c>
@@ -53770,7 +53770,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="270" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>272</v>
       </c>
@@ -53915,7 +53915,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="271" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>273</v>
       </c>
@@ -54062,7 +54062,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="272" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>274</v>
       </c>
@@ -54305,7 +54305,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="273" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>275</v>
       </c>
@@ -54534,7 +54534,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="274" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>276</v>
       </c>
@@ -54717,7 +54717,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="275" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>277</v>
       </c>
@@ -54942,7 +54942,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="276" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>278</v>
       </c>
@@ -55089,7 +55089,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="277" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>279</v>
       </c>
@@ -55314,7 +55314,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="278" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>280</v>
       </c>
@@ -55539,7 +55539,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="279" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>281</v>
       </c>
@@ -55684,7 +55684,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="280" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>282</v>
       </c>
@@ -55869,7 +55869,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="281" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>283</v>
       </c>
@@ -56098,7 +56098,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="282" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>284</v>
       </c>
@@ -56235,7 +56235,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="283" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>285</v>
       </c>
@@ -56418,7 +56418,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="284" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>286</v>
       </c>
@@ -56609,7 +56609,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="285" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>287</v>
       </c>
@@ -56746,7 +56746,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="286" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>288</v>
       </c>
@@ -56975,7 +56975,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="287" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>289</v>
       </c>
@@ -57166,7 +57166,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="288" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>290</v>
       </c>
@@ -57319,7 +57319,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="289" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>291</v>
       </c>
@@ -57544,7 +57544,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="290" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>292</v>
       </c>
@@ -57769,7 +57769,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="291" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>293</v>
       </c>
@@ -57908,7 +57908,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="292" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>294</v>
       </c>
@@ -58047,7 +58047,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="293" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>295</v>
       </c>
@@ -58296,7 +58296,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="294" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>296</v>
       </c>
@@ -58435,7 +58435,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="295" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>297</v>
       </c>
@@ -58622,7 +58622,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="296" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>298</v>
       </c>
@@ -58859,7 +58859,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="297" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>299</v>
       </c>
@@ -59042,7 +59042,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="298" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>300</v>
       </c>
@@ -59271,7 +59271,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="299" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>301</v>
       </c>
@@ -59418,7 +59418,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="300" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>302</v>
       </c>
@@ -59649,7 +59649,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="301" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>303</v>
       </c>
@@ -59838,7 +59838,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="302" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>304</v>
       </c>
@@ -60075,7 +60075,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="303" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>305</v>
       </c>
@@ -60304,7 +60304,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="304" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>306</v>
       </c>
@@ -60451,7 +60451,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="305" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>307</v>
       </c>
@@ -60634,7 +60634,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="306" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>308</v>
       </c>
@@ -60813,7 +60813,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="307" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>309</v>
       </c>
@@ -61064,7 +61064,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="308" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>310</v>
       </c>
@@ -61207,7 +61207,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="309" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>311</v>
       </c>
@@ -61398,7 +61398,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="310" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>312</v>
       </c>
@@ -61537,7 +61537,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="311" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>313</v>
       </c>
@@ -61632,7 +61632,7 @@
       <c r="CH311" s="1"/>
       <c r="CI311" s="1"/>
     </row>
-    <row r="312" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>314</v>
       </c>
@@ -61771,7 +61771,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="313" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>315</v>
       </c>
@@ -61954,7 +61954,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="314" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>316</v>
       </c>
@@ -62093,7 +62093,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="315" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>317</v>
       </c>
@@ -62240,7 +62240,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="316" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>318</v>
       </c>
@@ -62469,7 +62469,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="317" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>319</v>
       </c>
@@ -62728,7 +62728,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="318" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>320</v>
       </c>
@@ -62875,7 +62875,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="319" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>321</v>
       </c>
@@ -63014,7 +63014,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="320" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>322</v>
       </c>
@@ -63173,7 +63173,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="321" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>323</v>
       </c>
@@ -63376,7 +63376,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="322" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>324</v>
       </c>
@@ -63613,7 +63613,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="323" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>325</v>
       </c>
@@ -63800,7 +63800,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="324" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>326</v>
       </c>
@@ -64037,7 +64037,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="325" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>327</v>
       </c>
@@ -64266,7 +64266,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="326" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>328</v>
       </c>
@@ -64495,7 +64495,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="327" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>329</v>
       </c>
@@ -64748,7 +64748,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="328" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>330</v>
       </c>
@@ -64895,7 +64895,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="329" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>331</v>
       </c>
@@ -65042,7 +65042,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="330" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>332</v>
       </c>
@@ -65229,7 +65229,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="331" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>333</v>
       </c>
@@ -65376,7 +65376,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="332" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>334</v>
       </c>
@@ -65529,7 +65529,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="333" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>335</v>
       </c>
@@ -65766,7 +65766,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="334" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>336</v>
       </c>
@@ -66001,7 +66001,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="335" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>337</v>
       </c>
@@ -66248,7 +66248,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="336" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>338</v>
       </c>
@@ -66477,7 +66477,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="337" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>339</v>
       </c>
@@ -66670,7 +66670,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="338" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>340</v>
       </c>
@@ -66907,7 +66907,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="339" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>341</v>
       </c>
@@ -67052,7 +67052,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="340" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>342</v>
       </c>
@@ -67247,7 +67247,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="341" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>343</v>
       </c>
@@ -67394,7 +67394,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="342" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>344</v>
       </c>
@@ -67541,7 +67541,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="343" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>345</v>
       </c>
@@ -67772,7 +67772,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="344" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>346</v>
       </c>
@@ -67965,7 +67965,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="345" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>347</v>
       </c>
@@ -68166,7 +68166,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="346" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>348</v>
       </c>
@@ -68305,7 +68305,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="347" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>349</v>
       </c>
@@ -68496,7 +68496,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="348" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>350</v>
       </c>
@@ -68733,7 +68733,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="349" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>351</v>
       </c>
@@ -68962,7 +68962,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="350" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>352</v>
       </c>
@@ -69155,7 +69155,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="351" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>353</v>
       </c>
@@ -69390,7 +69390,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="352" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>354</v>
       </c>
@@ -69619,7 +69619,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="353" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>355</v>
       </c>
@@ -69874,7 +69874,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="354" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>356</v>
       </c>
@@ -70103,7 +70103,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="355" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>357</v>
       </c>
@@ -70288,7 +70288,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="356" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>358</v>
       </c>
@@ -70469,7 +70469,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="357" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>359</v>
       </c>
@@ -70616,7 +70616,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="358" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>360</v>
       </c>
@@ -70755,7 +70755,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="359" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>361</v>
       </c>
@@ -70890,7 +70890,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="360" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>362</v>
       </c>
@@ -71035,7 +71035,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="361" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>363</v>
       </c>
@@ -71174,7 +71174,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="362" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>364</v>
       </c>
@@ -71367,7 +71367,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="363" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>365</v>
       </c>
@@ -71596,7 +71596,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="364" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>366</v>
       </c>
@@ -71789,7 +71789,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="365" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>367</v>
       </c>
@@ -71936,7 +71936,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="366" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>368</v>
       </c>
@@ -72167,7 +72167,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="367" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>369</v>
       </c>
@@ -72306,7 +72306,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="368" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>370</v>
       </c>
@@ -72511,7 +72511,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="369" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>371</v>
       </c>
@@ -72742,7 +72742,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="370" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>372</v>
       </c>
@@ -72881,7 +72881,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="371" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>373</v>
       </c>
@@ -73120,7 +73120,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="372" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>374</v>
       </c>
@@ -73267,7 +73267,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="373" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -73412,7 +73412,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="374" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>376</v>
       </c>
@@ -73645,7 +73645,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="375" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>377</v>
       </c>
@@ -73874,7 +73874,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="376" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>378</v>
       </c>
@@ -74103,7 +74103,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="377" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>379</v>
       </c>
@@ -74238,7 +74238,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="378" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>380</v>
       </c>
@@ -74377,7 +74377,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="379" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>381</v>
       </c>
@@ -74514,7 +74514,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="380" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>382</v>
       </c>
@@ -74751,7 +74751,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="381" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>383</v>
       </c>
@@ -74982,7 +74982,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="382" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>384</v>
       </c>
@@ -75217,7 +75217,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="383" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>385</v>
       </c>
@@ -75360,7 +75360,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="384" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>

--- a/Data-Analytics/docs/FLEX DRIVE - Permítenos Conocerte.xlsx
+++ b/Data-Analytics/docs/FLEX DRIVE - Permítenos Conocerte.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\7SEMESTRE\FlexDrive\big data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leshi\OneDrive\Escritorio\University\006- Ninth Semester\000- Flex Drive\Flex-Drive\Data-Analytics\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE7762F7-991D-4111-844D-87249F76B51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A73D6F-BA2E-4FE1-A73C-1E6364533BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3189,42 +3189,15 @@
     <t>P12-Estado_Licencia_Conducción</t>
   </si>
   <si>
-    <t>P19-Beneficios_P2P</t>
-  </si>
-  <si>
-    <t>P20-Desventajas_P2P</t>
-  </si>
-  <si>
-    <t>P30-Interés_Propietario</t>
-  </si>
-  <si>
     <t>Hora_Inicio</t>
   </si>
   <si>
     <t>Hora_Fin</t>
   </si>
   <si>
-    <t>P18-Conoce_P2P</t>
-  </si>
-  <si>
     <t>P9-Frecuencia_Uso_Servicios_Públicos</t>
   </si>
   <si>
-    <t>P24N-Aspectos_Negativos_Exp2[P21]</t>
-  </si>
-  <si>
-    <t>P23N-Aspectos_Positivos_Exp[P21]</t>
-  </si>
-  <si>
-    <t>P22N-Forma_Renta[P21]</t>
-  </si>
-  <si>
-    <t>P17-Tipo_Veh]P15-Multi]</t>
-  </si>
-  <si>
-    <t>P16-Modo_Uso_Veh[P15-Multi]</t>
-  </si>
-  <si>
     <t>P17-Tipo_Veh[P15-U]</t>
   </si>
   <si>
@@ -3237,187 +3210,214 @@
     <t>P14-Frecuencia_Uso_Veh[P13]</t>
   </si>
   <si>
-    <t>P25-Ha_Tomado_En_Renta</t>
-  </si>
-  <si>
-    <t>P27N-Entidades_Donde_Rentó[P25]</t>
-  </si>
-  <si>
-    <t>P32[A]-Prioridad:Seguro_Vehicular[P30]</t>
-  </si>
-  <si>
-    <t>P32[B]-Prioridad:GPS_Vehicular[P30]</t>
-  </si>
-  <si>
-    <t>P32[C]-Prioridad:Autentificar_Todos_Los_Users[P30]</t>
-  </si>
-  <si>
-    <t>P32[E]-Prioridad:Comunicación_Directa_Cliente[P30]</t>
-  </si>
-  <si>
-    <t>P32[D]-Prioridad:Seguridad_Pagos_Plataforma[P30]</t>
-  </si>
-  <si>
-    <t>P32[F]-Prioridad:Apoyo_Precios[P30]</t>
-  </si>
-  <si>
-    <t>P32[G]-Prioridad:Contratos_Automáticos[P30]</t>
-  </si>
-  <si>
-    <t>P32[H]-Prioridad:Variedad_Pagos[P30]</t>
-  </si>
-  <si>
-    <t>P32[I]-Prioridad:Reseñas_Clientes[P30]</t>
-  </si>
-  <si>
-    <t>P32[J]-Prioridad:Contacto_FlexDrive[P30]</t>
-  </si>
-  <si>
-    <t>P32[K]-Prioridad:Asistencia_Legal[P30]</t>
-  </si>
-  <si>
-    <t>P32[L]-Prioridad:Apoyo_Cómo_Cobrar[P30]</t>
-  </si>
-  <si>
-    <t>P33N-Otras_Prioridades[P30]</t>
-  </si>
-  <si>
-    <t>P34-Modelo_Confianza_Multi[P30]</t>
-  </si>
-  <si>
-    <t>P35-Precio_Horas_Propietario_Multi[P30]</t>
-  </si>
-  <si>
-    <t>P36_Precio_Dia_Propietario_Multi[P30]</t>
-  </si>
-  <si>
-    <t>P37_Recibir_Pagos_Propietario[P30]</t>
-  </si>
-  <si>
-    <t>P40-Pago_FlexDrive_Propietarios[P30]</t>
-  </si>
-  <si>
-    <t>P39N-Otros_Motivos_Para_Rentar_Seguro[P30]</t>
-  </si>
-  <si>
-    <t>P41-Interés_Cliente</t>
-  </si>
-  <si>
-    <t>P43[A]-Prioridad:Comunicación_Propietario[P41]</t>
-  </si>
-  <si>
-    <t>P43[B]-Prioridad:Facilidad_Variedad_Pagos[P41]</t>
-  </si>
-  <si>
-    <t>P43[C]-Prioridad:Variedad_Seguros[P41]</t>
-  </si>
-  <si>
-    <t>P44N-Otras_Prioridades_Para_Tomar_en_Renta[41]</t>
-  </si>
-  <si>
-    <t>P45-Precio_Horas_Cliente_Multi[P41]</t>
-  </si>
-  <si>
-    <t>P46-Precio_Dia_Cliente_Multi[P41]</t>
-  </si>
-  <si>
-    <t>P47[A]-Confianza:Negociar_con_Propietario[P41]</t>
-  </si>
-  <si>
-    <t>P47[C]-Confianza:Medio_de_Pago_Recibido[P41]</t>
-  </si>
-  <si>
-    <t>P47[E]-Confianza:Reseñas_Propietario[P41]</t>
-  </si>
-  <si>
-    <t>P47[F]-Confianza:Claridad_Contrato[P41]</t>
-  </si>
-  <si>
-    <t>P49-Idea_FlexDrive</t>
-  </si>
-  <si>
-    <t>P48N-Otros_Puntos_Confianza_para_Rentar[P41]</t>
-  </si>
-  <si>
-    <t>P50-Usaría_FlexDrive…</t>
-  </si>
-  <si>
-    <t>P51-Preferencias_para_Comunicarse_con_FlexDrive</t>
-  </si>
-  <si>
     <t>P3-País</t>
   </si>
   <si>
     <t>P13-Posee_Veh_Propio</t>
   </si>
   <si>
-    <t>P21-Ha_Rentado_Su_Veh</t>
-  </si>
-  <si>
-    <t>P26N-Lugar_donde_Rentó[P25]</t>
-  </si>
-  <si>
-    <t>P29N-Desventajas_Experiencia[P25]</t>
-  </si>
-  <si>
-    <t>P28N-Beneficios_Experiencia[P25]</t>
-  </si>
-  <si>
-    <t>P31-Modo_Preferido_Renta_Veh[P30]</t>
-  </si>
-  <si>
-    <t>P38[A]-Confianza:Edad_Experiencia_Cliente[P30]</t>
-  </si>
-  <si>
-    <t>P38[B]-Confianza:Antecedentes_Cliente[P30]</t>
-  </si>
-  <si>
-    <t>P38[C]-Confianza:Medio_Pago_Ofertado[P30]</t>
-  </si>
-  <si>
-    <t>P38[D]-Confianza:Calificación_Que_Tiene_El_Cliente[P30]</t>
-  </si>
-  <si>
-    <t>P38[E]-Confianza:Motivo_Solicitud[P30]</t>
-  </si>
-  <si>
-    <t>P42-Modo_Preferido_Renta_Veh[P41]</t>
-  </si>
-  <si>
-    <t>P43[D]-Prioridad:Verificación_Usuarios[P41]</t>
-  </si>
-  <si>
-    <t>P43[E]-Prioridad:Apoyo_Dudas[P42]</t>
-  </si>
-  <si>
-    <t>P43[F]-Prioridad:Precios_y_Ofertas[P41]</t>
-  </si>
-  <si>
-    <t>P43[G]-Prioridad:Comunicación_FlexDrive[P41]</t>
-  </si>
-  <si>
-    <t>P43[H]-Prioridad:Reseñar_Propietarios[P41]</t>
-  </si>
-  <si>
-    <t>P43[I]-Prioridad:Modelo_Renta_en_15MINS[P41]</t>
-  </si>
-  <si>
-    <t>P43[J]-Prioridad:Modelo_Negociación[P41]</t>
-  </si>
-  <si>
-    <t>P47[B]-Confianza:Antigüedad_Veh[P41]</t>
-  </si>
-  <si>
-    <t>P47[D]-Confianza:Reseñas_Veh[P41]</t>
-  </si>
-  <si>
-    <t>P47[G]-Confianza:Punto_Entrega_Devolución_Vehículo[P41]</t>
-  </si>
-  <si>
-    <t>P47[H]-Confianza:Revisión_Tecnicomecánica_Veh[P41]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q estén óptimas condiciones </t>
+  </si>
+  <si>
+    <t>P18-Modo_Uso_Veh[P15-Multi]</t>
+  </si>
+  <si>
+    <t>P19-Tipo_Veh]P15-Multi]</t>
+  </si>
+  <si>
+    <t>P20-Conoce_P2P</t>
+  </si>
+  <si>
+    <t>P21-Beneficios_P2P</t>
+  </si>
+  <si>
+    <t>P22-Desventajas_P2P</t>
+  </si>
+  <si>
+    <t>P23-Ha_Rentado_Su_Veh</t>
+  </si>
+  <si>
+    <t>P24N-Forma_Renta[P21]</t>
+  </si>
+  <si>
+    <t>P25N-Aspectos_Positivos_Exp[P21]</t>
+  </si>
+  <si>
+    <t>P26N-Aspectos_Negativos_Exp2[P21]</t>
+  </si>
+  <si>
+    <t>P27-Ha_Tomado_En_Renta</t>
+  </si>
+  <si>
+    <t>P28N-Lugar_donde_Rentó[P25]</t>
+  </si>
+  <si>
+    <t>P29N-Entidades_Donde_Rentó[P25]</t>
+  </si>
+  <si>
+    <t>P30N-Beneficios_Experiencia[P25]</t>
+  </si>
+  <si>
+    <t>P31N-Desventajas_Experiencia[P25]</t>
+  </si>
+  <si>
+    <t>P32-Interés_Propietario</t>
+  </si>
+  <si>
+    <t>P33-Modo_Preferido_Renta_Veh[P30]</t>
+  </si>
+  <si>
+    <t>P34[A]-Prioridad:Seguro_Vehicular[P30]</t>
+  </si>
+  <si>
+    <t>P34[B]-Prioridad:GPS_Vehicular[P30]</t>
+  </si>
+  <si>
+    <t>P34[C]-Prioridad:Autentificar_Todos_Los_Users[P30]</t>
+  </si>
+  <si>
+    <t>P34[D]-Prioridad:Seguridad_Pagos_Plataforma[P30]</t>
+  </si>
+  <si>
+    <t>P34[E]-Prioridad:Comunicación_Directa_Cliente[P30]</t>
+  </si>
+  <si>
+    <t>P34[F]-Prioridad:Apoyo_Precios[P30]</t>
+  </si>
+  <si>
+    <t>P34[G]-Prioridad:Contratos_Automáticos[P30]</t>
+  </si>
+  <si>
+    <t>P34[H]-Prioridad:Variedad_Pagos[P30]</t>
+  </si>
+  <si>
+    <t>P34[I]-Prioridad:Reseñas_Clientes[P30]</t>
+  </si>
+  <si>
+    <t>P34[J]-Prioridad:Contacto_FlexDrive[P30]</t>
+  </si>
+  <si>
+    <t>P34[K]-Prioridad:Asistencia_Legal[P30]</t>
+  </si>
+  <si>
+    <t>P34[L]-Prioridad:Apoyo_Cómo_Cobrar[P30]</t>
+  </si>
+  <si>
+    <t>P35N-Otras_Prioridades[P30]</t>
+  </si>
+  <si>
+    <t>P36-Modelo_Confianza_Multi[P30]</t>
+  </si>
+  <si>
+    <t>P37-Precio_Horas_Propietario_Multi[P30]</t>
+  </si>
+  <si>
+    <t>P38_Precio_Dia_Propietario_Multi[P30]</t>
+  </si>
+  <si>
+    <t>P39_Recibir_Pagos_Propietario[P30]</t>
+  </si>
+  <si>
+    <t>P40[A]-Confianza:Edad_Experiencia_Cliente[P30]</t>
+  </si>
+  <si>
+    <t>P40[B]-Confianza:Antecedentes_Cliente[P30]</t>
+  </si>
+  <si>
+    <t>P40[C]-Confianza:Medio_Pago_Ofertado[P30]</t>
+  </si>
+  <si>
+    <t>P40[D]-Confianza:Calificación_Que_Tiene_El_Cliente[P30]</t>
+  </si>
+  <si>
+    <t>P40[E]-Confianza:Motivo_Solicitud[P30]</t>
+  </si>
+  <si>
+    <t>P41N-Otros_Motivos_Para_Rentar_Seguro[P30]</t>
+  </si>
+  <si>
+    <t>P42-Pago_FlexDrive_Propietarios[P30]</t>
+  </si>
+  <si>
+    <t>P43-Interés_Cliente</t>
+  </si>
+  <si>
+    <t>P44-Modo_Preferido_Renta_Veh[P41]</t>
+  </si>
+  <si>
+    <t>P45[A]-Prioridad:Comunicación_Propietario[P41]</t>
+  </si>
+  <si>
+    <t>P45[B]-Prioridad:Facilidad_Variedad_Pagos[P41]</t>
+  </si>
+  <si>
+    <t>P45[C]-Prioridad:Variedad_Seguros[P41]</t>
+  </si>
+  <si>
+    <t>P45[D]-Prioridad:Verificación_Usuarios[P41]</t>
+  </si>
+  <si>
+    <t>P45[E]-Prioridad:Apoyo_Dudas[P42]</t>
+  </si>
+  <si>
+    <t>P45[F]-Prioridad:Precios_y_Ofertas[P41]</t>
+  </si>
+  <si>
+    <t>P45[G]-Prioridad:Comunicación_FlexDrive[P41]</t>
+  </si>
+  <si>
+    <t>P45[H]-Prioridad:Reseñar_Propietarios[P41]</t>
+  </si>
+  <si>
+    <t>P45[I]-Prioridad:Modelo_Renta_en_15MINS[P41]</t>
+  </si>
+  <si>
+    <t>P45[J]-Prioridad:Modelo_Negociación[P41]</t>
+  </si>
+  <si>
+    <t>P46N-Otras_Prioridades_Para_Tomar_en_Renta[41]</t>
+  </si>
+  <si>
+    <t>P47-Precio_Horas_Cliente_Multi[P41]</t>
+  </si>
+  <si>
+    <t>P48-Precio_Dia_Cliente_Multi[P41]</t>
+  </si>
+  <si>
+    <t>P49[A]-Confianza:Negociar_con_Propietario[P41]</t>
+  </si>
+  <si>
+    <t>P49[B]-Confianza:Antigüedad_Veh[P41]</t>
+  </si>
+  <si>
+    <t>P49[C]-Confianza:Medio_de_Pago_Recibido[P41]</t>
+  </si>
+  <si>
+    <t>P49[D]-Confianza:Reseñas_Veh[P41]</t>
+  </si>
+  <si>
+    <t>P49[E]-Confianza:Reseñas_Propietario[P41]</t>
+  </si>
+  <si>
+    <t>P49[F]-Confianza:Claridad_Contrato[P41]</t>
+  </si>
+  <si>
+    <t>P49[G]-Confianza:Punto_Entrega_Devolución_Vehículo[P41]</t>
+  </si>
+  <si>
+    <t>P49[H]-Confianza:Revisión_Tecnicomecánica_Veh[P41]</t>
+  </si>
+  <si>
+    <t>P50N-Otros_Puntos_Confianza_para_Rentar[P41]</t>
+  </si>
+  <si>
+    <t>P51-Idea_FlexDrive</t>
+  </si>
+  <si>
+    <t>P52-Usaría_FlexDrive…</t>
+  </si>
+  <si>
+    <t>P53-Preferencias_para_Comunicarse_con_FlexDrive</t>
   </si>
 </sst>
 </file>
@@ -3909,469 +3909,469 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="P16-Modo_Uso_Veh[P15-Multi]" dataDxfId="66">
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="P18-Modo_Uso_Veh[P15-Multi]" dataDxfId="66">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r59161771cef24e2bb66cb29da5f3451c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="P17-Tipo_Veh]P15-Multi]" dataDxfId="65">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="P19-Tipo_Veh]P15-Multi]" dataDxfId="65">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r85672192d2374f788d186bcc5835c724"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="P18-Conoce_P2P" dataDxfId="64">
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="P20-Conoce_P2P" dataDxfId="64">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra31041ccce5b46ed8105683abeef1f0a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="P19-Beneficios_P2P" dataDxfId="63">
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="P21-Beneficios_P2P" dataDxfId="63">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re41b537c8ba54615b800c9714a249b4d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="P20-Desventajas_P2P" dataDxfId="62">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="P22-Desventajas_P2P" dataDxfId="62">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rde6549e24a954dc2b8797e32afc75d1f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="P21-Ha_Rentado_Su_Veh" dataDxfId="61">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="P23-Ha_Rentado_Su_Veh" dataDxfId="61">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5e3a5d404a464d8da96b8b00c99d2dce"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="P22N-Forma_Renta[P21]" dataDxfId="60">
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="P24N-Forma_Renta[P21]" dataDxfId="60">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfd0284a5786546ee8e652df5dc54bb00"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="P23N-Aspectos_Positivos_Exp[P21]" dataDxfId="59">
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="P25N-Aspectos_Positivos_Exp[P21]" dataDxfId="59">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r18c62dfbddcc4a579b16a946cb15ad79"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="P24N-Aspectos_Negativos_Exp2[P21]" dataDxfId="58">
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="P26N-Aspectos_Negativos_Exp2[P21]" dataDxfId="58">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re5871aa07cf8438ab7f6352fbe5e0727"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="P25-Ha_Tomado_En_Renta" dataDxfId="57">
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="P27-Ha_Tomado_En_Renta" dataDxfId="57">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf682f1ce3b244b0d9e2b0faae42d2d6c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="90" xr3:uid="{6F90A585-A7C4-4869-8AC6-9668CE6299BA}" name="P26N-Lugar_donde_Rentó[P25]" dataDxfId="56">
+    <tableColumn id="90" xr3:uid="{6F90A585-A7C4-4869-8AC6-9668CE6299BA}" name="P28N-Lugar_donde_Rentó[P25]" dataDxfId="56">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1b29d4ac37ee4bfd9b59d7e72b3e3f1f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="P27N-Entidades_Donde_Rentó[P25]" dataDxfId="55">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="P29N-Entidades_Donde_Rentó[P25]" dataDxfId="55">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r83c3fa0f12d9477c8d56a6bff31f62e4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="P28N-Beneficios_Experiencia[P25]" dataDxfId="54">
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="P30N-Beneficios_Experiencia[P25]" dataDxfId="54">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r3968670305ac4ec2aa72837e3f164f9b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="P29N-Desventajas_Experiencia[P25]" dataDxfId="53">
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="P31N-Desventajas_Experiencia[P25]" dataDxfId="53">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rceffe316e4624836af7749977ce8e805"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="P30-Interés_Propietario" dataDxfId="52">
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="P32-Interés_Propietario" dataDxfId="52">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0bb794ae10ef45b7b49d94611644a7e0"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="P31-Modo_Preferido_Renta_Veh[P30]" dataDxfId="51">
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="P33-Modo_Preferido_Renta_Veh[P30]" dataDxfId="51">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rea498a1a4a5049d8bf749eac0c1787d8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="P32[A]-Prioridad:Seguro_Vehicular[P30]" dataDxfId="50">
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="P34[A]-Prioridad:Seguro_Vehicular[P30]" dataDxfId="50">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfb650a03a8864672bc6a3c61441b33ee"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="P32[B]-Prioridad:GPS_Vehicular[P30]" dataDxfId="49">
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="P34[B]-Prioridad:GPS_Vehicular[P30]" dataDxfId="49">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r034a8f449c3c45f3bc431a2f888ab68e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="P32[C]-Prioridad:Autentificar_Todos_Los_Users[P30]" dataDxfId="48">
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="P34[C]-Prioridad:Autentificar_Todos_Los_Users[P30]" dataDxfId="48">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1c59a4f621364b38b271ddcdcc5e44ec"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="P32[D]-Prioridad:Seguridad_Pagos_Plataforma[P30]" dataDxfId="47">
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="P34[D]-Prioridad:Seguridad_Pagos_Plataforma[P30]" dataDxfId="47">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r24bea2ef36834659bd8ffc294f882fc8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="P32[E]-Prioridad:Comunicación_Directa_Cliente[P30]" dataDxfId="46">
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="P34[E]-Prioridad:Comunicación_Directa_Cliente[P30]" dataDxfId="46">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc1d89a242aa84b43be44f8e7e28c82a1"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="P32[F]-Prioridad:Apoyo_Precios[P30]" dataDxfId="45">
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="P34[F]-Prioridad:Apoyo_Precios[P30]" dataDxfId="45">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rad9e48be32804b3bad9f6dd5e9311b6b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="P32[G]-Prioridad:Contratos_Automáticos[P30]" dataDxfId="44">
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="P34[G]-Prioridad:Contratos_Automáticos[P30]" dataDxfId="44">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7f7fafe3b7e14df5a6de19560e7c2de9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="P32[H]-Prioridad:Variedad_Pagos[P30]" dataDxfId="43">
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="P34[H]-Prioridad:Variedad_Pagos[P30]" dataDxfId="43">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r53157258b245497da117dc27044fa03a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="P32[I]-Prioridad:Reseñas_Clientes[P30]" dataDxfId="42">
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="P34[I]-Prioridad:Reseñas_Clientes[P30]" dataDxfId="42">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r2fbc8d445dcf40ffbc2ca7bc4c4b1975"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="P32[J]-Prioridad:Contacto_FlexDrive[P30]" dataDxfId="41">
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="P34[J]-Prioridad:Contacto_FlexDrive[P30]" dataDxfId="41">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r48828849b761400b9a8421310f726e46"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="P32[K]-Prioridad:Asistencia_Legal[P30]" dataDxfId="40">
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="P34[K]-Prioridad:Asistencia_Legal[P30]" dataDxfId="40">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r8e67de98af4b4f868614569f8fa4557a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="P32[L]-Prioridad:Apoyo_Cómo_Cobrar[P30]" dataDxfId="39">
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="P34[L]-Prioridad:Apoyo_Cómo_Cobrar[P30]" dataDxfId="39">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0594be0e3fda4932af60966190002a8f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="P33N-Otras_Prioridades[P30]" dataDxfId="38">
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="P35N-Otras_Prioridades[P30]" dataDxfId="38">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r02915f7f329548d1a6c59de6f81aff8a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="P34-Modelo_Confianza_Multi[P30]" dataDxfId="37">
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="P36-Modelo_Confianza_Multi[P30]" dataDxfId="37">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r33bdfdf9d5ad45bd87d377b9e3a13b01"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="P35-Precio_Horas_Propietario_Multi[P30]" dataDxfId="36">
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="P37-Precio_Horas_Propietario_Multi[P30]" dataDxfId="36">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r266fe3fbff6c495db4ac7fa2bd3bc0af"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="P36_Precio_Dia_Propietario_Multi[P30]" dataDxfId="35">
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="P38_Precio_Dia_Propietario_Multi[P30]" dataDxfId="35">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9e4ceeed77da4910be745d63d011f39f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="P37_Recibir_Pagos_Propietario[P30]" dataDxfId="34">
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="P39_Recibir_Pagos_Propietario[P30]" dataDxfId="34">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r70df6c2d792c462eb739a27a3d069899"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="P38[A]-Confianza:Edad_Experiencia_Cliente[P30]" dataDxfId="33">
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="P40[A]-Confianza:Edad_Experiencia_Cliente[P30]" dataDxfId="33">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6c5bafde9007451fb29b839f8c49a15e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="P38[B]-Confianza:Antecedentes_Cliente[P30]" dataDxfId="32">
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="P40[B]-Confianza:Antecedentes_Cliente[P30]" dataDxfId="32">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7613b42036ce49e2a3ddb8eb05472462"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="P38[C]-Confianza:Medio_Pago_Ofertado[P30]" dataDxfId="31">
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="P40[C]-Confianza:Medio_Pago_Ofertado[P30]" dataDxfId="31">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb4fed81eec754a04b3d8022b7897b0f3"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="P38[D]-Confianza:Calificación_Que_Tiene_El_Cliente[P30]" dataDxfId="30">
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="P40[D]-Confianza:Calificación_Que_Tiene_El_Cliente[P30]" dataDxfId="30">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb4351db70e9749ceace1dcdd37651823"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="P38[E]-Confianza:Motivo_Solicitud[P30]" dataDxfId="29">
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="P40[E]-Confianza:Motivo_Solicitud[P30]" dataDxfId="29">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r63750ac42fe24fbc93ff53a0c20992a6"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="P39N-Otros_Motivos_Para_Rentar_Seguro[P30]" dataDxfId="28">
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="P41N-Otros_Motivos_Para_Rentar_Seguro[P30]" dataDxfId="28">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r895e06d449d54205864d9779294f6793"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="P40-Pago_FlexDrive_Propietarios[P30]" dataDxfId="27">
+    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="P42-Pago_FlexDrive_Propietarios[P30]" dataDxfId="27">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rba74ffcf8ce64692a961aa00332beeeb"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="P41-Interés_Cliente" dataDxfId="26">
+    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="P43-Interés_Cliente" dataDxfId="26">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rcd1f6cfa70b540458954df8693089822"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="P42-Modo_Preferido_Renta_Veh[P41]" dataDxfId="25">
+    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="P44-Modo_Preferido_Renta_Veh[P41]" dataDxfId="25">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rcbdd13d0d95e400d88acab0c8ecc59fb"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="P43[A]-Prioridad:Comunicación_Propietario[P41]" dataDxfId="24">
+    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="P45[A]-Prioridad:Comunicación_Propietario[P41]" dataDxfId="24">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc5acdb89810d4746939091eb0b277494"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="66" xr3:uid="{00000000-0010-0000-0000-000042000000}" name="P43[B]-Prioridad:Facilidad_Variedad_Pagos[P41]" dataDxfId="23">
+    <tableColumn id="66" xr3:uid="{00000000-0010-0000-0000-000042000000}" name="P45[B]-Prioridad:Facilidad_Variedad_Pagos[P41]" dataDxfId="23">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc3cdf966efbb45dbacb0501deb01c314"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="67" xr3:uid="{00000000-0010-0000-0000-000043000000}" name="P43[C]-Prioridad:Variedad_Seguros[P41]" dataDxfId="22">
+    <tableColumn id="67" xr3:uid="{00000000-0010-0000-0000-000043000000}" name="P45[C]-Prioridad:Variedad_Seguros[P41]" dataDxfId="22">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="raf7e2ab47b2e452596e260b4cd40ec4f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="68" xr3:uid="{00000000-0010-0000-0000-000044000000}" name="P43[D]-Prioridad:Verificación_Usuarios[P41]" dataDxfId="21">
+    <tableColumn id="68" xr3:uid="{00000000-0010-0000-0000-000044000000}" name="P45[D]-Prioridad:Verificación_Usuarios[P41]" dataDxfId="21">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb7fe92bc8ba7474d810e03fbb098374f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="69" xr3:uid="{00000000-0010-0000-0000-000045000000}" name="P43[E]-Prioridad:Apoyo_Dudas[P42]" dataDxfId="20">
+    <tableColumn id="69" xr3:uid="{00000000-0010-0000-0000-000045000000}" name="P45[E]-Prioridad:Apoyo_Dudas[P42]" dataDxfId="20">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r04dfe81d5a5a43fa93e5aea6c59b96a4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="70" xr3:uid="{00000000-0010-0000-0000-000046000000}" name="P43[F]-Prioridad:Precios_y_Ofertas[P41]" dataDxfId="19">
+    <tableColumn id="70" xr3:uid="{00000000-0010-0000-0000-000046000000}" name="P45[F]-Prioridad:Precios_y_Ofertas[P41]" dataDxfId="19">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r727126039fa14e019d115c02fb7f1fd2"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="71" xr3:uid="{00000000-0010-0000-0000-000047000000}" name="P43[G]-Prioridad:Comunicación_FlexDrive[P41]" dataDxfId="18">
+    <tableColumn id="71" xr3:uid="{00000000-0010-0000-0000-000047000000}" name="P45[G]-Prioridad:Comunicación_FlexDrive[P41]" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r881f018dcf174ac7a11b214c598a175a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="72" xr3:uid="{00000000-0010-0000-0000-000048000000}" name="P43[H]-Prioridad:Reseñar_Propietarios[P41]" dataDxfId="17">
+    <tableColumn id="72" xr3:uid="{00000000-0010-0000-0000-000048000000}" name="P45[H]-Prioridad:Reseñar_Propietarios[P41]" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5a3f35b140d74758a9234e65fd74d859"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="P43[I]-Prioridad:Modelo_Renta_en_15MINS[P41]" dataDxfId="16">
+    <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="P45[I]-Prioridad:Modelo_Renta_en_15MINS[P41]" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r3ac1ad4866bc4e449a3a596c780f1a70"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="P43[J]-Prioridad:Modelo_Negociación[P41]" dataDxfId="15">
+    <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="P45[J]-Prioridad:Modelo_Negociación[P41]" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r33b7716d71d64483ba788a7ca6039dfb"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="P44N-Otras_Prioridades_Para_Tomar_en_Renta[41]" dataDxfId="14">
+    <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="P46N-Otras_Prioridades_Para_Tomar_en_Renta[41]" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r8ace7defcef5443d849033f62932fcdd"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="76" xr3:uid="{00000000-0010-0000-0000-00004C000000}" name="P45-Precio_Horas_Cliente_Multi[P41]" dataDxfId="13">
+    <tableColumn id="76" xr3:uid="{00000000-0010-0000-0000-00004C000000}" name="P47-Precio_Horas_Cliente_Multi[P41]" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf3f0385389e141489501b50e234a3da9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{00000000-0010-0000-0000-00004D000000}" name="P46-Precio_Dia_Cliente_Multi[P41]" dataDxfId="12">
+    <tableColumn id="77" xr3:uid="{00000000-0010-0000-0000-00004D000000}" name="P48-Precio_Dia_Cliente_Multi[P41]" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r06d6937a25a148d9b5c0b5538b8244e4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="78" xr3:uid="{00000000-0010-0000-0000-00004E000000}" name="P47[A]-Confianza:Negociar_con_Propietario[P41]" dataDxfId="11">
+    <tableColumn id="78" xr3:uid="{00000000-0010-0000-0000-00004E000000}" name="P49[A]-Confianza:Negociar_con_Propietario[P41]" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r820c96033e8e437e87691beb584d7faa"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="79" xr3:uid="{00000000-0010-0000-0000-00004F000000}" name="P47[B]-Confianza:Antigüedad_Veh[P41]" dataDxfId="10">
+    <tableColumn id="79" xr3:uid="{00000000-0010-0000-0000-00004F000000}" name="P49[B]-Confianza:Antigüedad_Veh[P41]" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r038029bfde524413be8bb14ee83cc06f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="80" xr3:uid="{00000000-0010-0000-0000-000050000000}" name="P47[C]-Confianza:Medio_de_Pago_Recibido[P41]" dataDxfId="9">
+    <tableColumn id="80" xr3:uid="{00000000-0010-0000-0000-000050000000}" name="P49[C]-Confianza:Medio_de_Pago_Recibido[P41]" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r60f1ce968783450ebe1b73e776f17c65"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="81" xr3:uid="{00000000-0010-0000-0000-000051000000}" name="P47[D]-Confianza:Reseñas_Veh[P41]" dataDxfId="8">
+    <tableColumn id="81" xr3:uid="{00000000-0010-0000-0000-000051000000}" name="P49[D]-Confianza:Reseñas_Veh[P41]" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r261a70afa9254bcd8786df637a49fcf5"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="82" xr3:uid="{00000000-0010-0000-0000-000052000000}" name="P47[E]-Confianza:Reseñas_Propietario[P41]" dataDxfId="7">
+    <tableColumn id="82" xr3:uid="{00000000-0010-0000-0000-000052000000}" name="P49[E]-Confianza:Reseñas_Propietario[P41]" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r310bea174fdb46a48a309402199900de"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="83" xr3:uid="{00000000-0010-0000-0000-000053000000}" name="P47[F]-Confianza:Claridad_Contrato[P41]" dataDxfId="6">
+    <tableColumn id="83" xr3:uid="{00000000-0010-0000-0000-000053000000}" name="P49[F]-Confianza:Claridad_Contrato[P41]" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5b07ccaa3dba40c68cf482eded3f5d9e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="88" xr3:uid="{EF9E9831-1475-4A1E-9E10-28C936F602EE}" name="P47[G]-Confianza:Punto_Entrega_Devolución_Vehículo[P41]" dataDxfId="5">
+    <tableColumn id="88" xr3:uid="{EF9E9831-1475-4A1E-9E10-28C936F602EE}" name="P49[G]-Confianza:Punto_Entrega_Devolución_Vehículo[P41]" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r190c41f474664fdaa30da7c296d8f9d9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="89" xr3:uid="{FFC4B32B-10D7-4F39-B935-8E941D5F425D}" name="P47[H]-Confianza:Revisión_Tecnicomecánica_Veh[P41]" dataDxfId="4">
+    <tableColumn id="89" xr3:uid="{FFC4B32B-10D7-4F39-B935-8E941D5F425D}" name="P49[H]-Confianza:Revisión_Tecnicomecánica_Veh[P41]" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r13dad7a60be045efb40589a8e93a6a20"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="84" xr3:uid="{00000000-0010-0000-0000-000054000000}" name="P48N-Otros_Puntos_Confianza_para_Rentar[P41]" dataDxfId="3">
+    <tableColumn id="84" xr3:uid="{00000000-0010-0000-0000-000054000000}" name="P50N-Otros_Puntos_Confianza_para_Rentar[P41]" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r95b55d266649436b9b270e44ddf0755d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="85" xr3:uid="{00000000-0010-0000-0000-000055000000}" name="P49-Idea_FlexDrive" dataDxfId="2">
+    <tableColumn id="85" xr3:uid="{00000000-0010-0000-0000-000055000000}" name="P51-Idea_FlexDrive" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re1509f737f19430b8b51d3aa1dc14d55"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="86" xr3:uid="{00000000-0010-0000-0000-000056000000}" name="P50-Usaría_FlexDrive…" dataDxfId="1">
+    <tableColumn id="86" xr3:uid="{00000000-0010-0000-0000-000056000000}" name="P52-Usaría_FlexDrive…" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r3f3f56969427408d847b5e353694570a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="87" xr3:uid="{00000000-0010-0000-0000-000057000000}" name="P51-Preferencias_para_Comunicarse_con_FlexDrive" dataDxfId="0">
+    <tableColumn id="87" xr3:uid="{00000000-0010-0000-0000-000057000000}" name="P53-Preferencias_para_Comunicarse_con_FlexDrive" dataDxfId="0">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra9c8ccd9f29d44f28a6ad40177d9bbd9"/>
@@ -4777,104 +4777,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CI384"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="104" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="90.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="90.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="137.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="73.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="137.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="70" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="59.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="40.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="125.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="67.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="125.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="67.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="255.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="240.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="72.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="217.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="223.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="96.5546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="240.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="72.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="217.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="223.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="96.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="255.7109375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="44" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="113" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="39.44140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="50.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="49.88671875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="49.85546875" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="51" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="44.88671875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="37.88671875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="40.5546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="42.109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="255.6640625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="240.33203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="132.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="116.6640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="255.6640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="47.5546875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="44.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="44.5546875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="55.6640625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="129.33203125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="155.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="240.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="132.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="116.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="55.7109375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="129.28515625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="155.28515625" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="43" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="73.88671875" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="46.88671875" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="73.85546875" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="39.5703125" bestFit="1" customWidth="1"/>
     <col min="69" max="69" width="46" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="47.5546875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="42.109375" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="255.6640625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="132.44140625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="128.6640625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="47.5546875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="47.5546875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="42.44140625" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="40.109375" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="57.88671875" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="52.88671875" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="255.6640625" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="132.42578125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="128.7109375" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="86" max="86" width="74" bestFit="1" customWidth="1"/>
     <col min="87" max="87" width="161" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="C1" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="D1" t="s">
         <v>1040</v>
@@ -4883,7 +4883,7 @@
         <v>1041</v>
       </c>
       <c r="F1" t="s">
-        <v>1102</v>
+        <v>1057</v>
       </c>
       <c r="G1" t="s">
         <v>1042</v>
@@ -4901,7 +4901,7 @@
         <v>1046</v>
       </c>
       <c r="L1" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="M1" t="s">
         <v>1047</v>
@@ -4913,223 +4913,223 @@
         <v>1049</v>
       </c>
       <c r="P1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AW1" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="BK1" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="BL1" s="6" t="s">
         <v>1103</v>
       </c>
-      <c r="Q1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="S1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="U1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="V1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="W1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="X1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="Z1" t="s">
+      <c r="BM1" s="6" t="s">
         <v>1104</v>
       </c>
-      <c r="AA1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="AE1" s="3" t="s">
+      <c r="BN1" t="s">
         <v>1105</v>
       </c>
-      <c r="AF1" s="3" t="s">
-        <v>1067</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="BO1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="BP1" t="s">
         <v>1107</v>
       </c>
-      <c r="AH1" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>1052</v>
-      </c>
-      <c r="AJ1" t="s">
+      <c r="BQ1" t="s">
         <v>1108</v>
       </c>
-      <c r="AK1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>1070</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="AW1" s="5" t="s">
-        <v>1080</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="BB1" t="s">
+      <c r="BR1" t="s">
         <v>1109</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BS1" t="s">
         <v>1110</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BT1" t="s">
         <v>1111</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BU1" t="s">
         <v>1112</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BV1" t="s">
         <v>1113</v>
       </c>
-      <c r="BG1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="BJ1" t="s">
+      <c r="BW1" t="s">
         <v>1114</v>
       </c>
-      <c r="BK1" s="6" t="s">
-        <v>1088</v>
-      </c>
-      <c r="BL1" s="6" t="s">
-        <v>1089</v>
-      </c>
-      <c r="BM1" s="6" t="s">
-        <v>1090</v>
-      </c>
-      <c r="BN1" t="s">
+      <c r="BX1" t="s">
         <v>1115</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BY1" t="s">
         <v>1116</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BZ1" t="s">
         <v>1117</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="CA1" t="s">
         <v>1118</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="CB1" t="s">
         <v>1119</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="CC1" t="s">
         <v>1120</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="CD1" t="s">
         <v>1121</v>
       </c>
-      <c r="BU1" t="s">
-        <v>1091</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="BY1" t="s">
+      <c r="CE1" t="s">
         <v>1122</v>
       </c>
-      <c r="BZ1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="CA1" t="s">
+      <c r="CF1" t="s">
         <v>1123</v>
       </c>
-      <c r="CB1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="CD1" t="s">
+      <c r="CG1" t="s">
         <v>1124</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CH1" t="s">
         <v>1125</v>
       </c>
-      <c r="CF1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>1100</v>
-      </c>
       <c r="CI1" t="s">
-        <v>1101</v>
+        <v>1126</v>
       </c>
     </row>
-    <row r="2" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>16</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>17</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>18</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>19</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="18" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>20</v>
       </c>
@@ -7422,7 +7422,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>21</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>22</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>23</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>24</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>27</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>28</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>29</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>30</v>
       </c>
@@ -8984,7 +8984,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="29" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>31</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="30" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>32</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>33</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>34</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>35</v>
       </c>
@@ -9900,7 +9900,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>36</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="35" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>37</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>38</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>39</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>40</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="39" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>41</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="40" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>42</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="41" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>43</v>
       </c>
@@ -11343,7 +11343,7 @@
       <c r="CH41" s="1"/>
       <c r="CI41" s="1"/>
     </row>
-    <row r="42" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>44</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>45</v>
       </c>
@@ -11713,7 +11713,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="44" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>46</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>47</v>
       </c>
@@ -12125,7 +12125,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="46" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>48</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="47" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>49</v>
       </c>
@@ -12494,7 +12494,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="48" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>50</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="49" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>51</v>
       </c>
@@ -12864,7 +12864,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="50" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>52</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="51" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>53</v>
       </c>
@@ -13276,7 +13276,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="52" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>54</v>
       </c>
@@ -13471,7 +13471,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="53" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>55</v>
       </c>
@@ -13666,7 +13666,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="54" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>56</v>
       </c>
@@ -13899,7 +13899,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="55" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>57</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>58</v>
       </c>
@@ -14229,7 +14229,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="57" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>59</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="58" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>60</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="59" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>61</v>
       </c>
@@ -14860,7 +14860,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="60" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>62</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="61" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>63</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="62" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>64</v>
       </c>
@@ -15439,7 +15439,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="63" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>65</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="64" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>66</v>
       </c>
@@ -15825,7 +15825,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="65" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>67</v>
       </c>
@@ -15964,7 +15964,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="66" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>68</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="67" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>69</v>
       </c>
@@ -16348,7 +16348,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="68" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>70</v>
       </c>
@@ -16493,7 +16493,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="69" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>71</v>
       </c>
@@ -16678,7 +16678,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="70" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>72</v>
       </c>
@@ -16919,7 +16919,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>73</v>
       </c>
@@ -17162,7 +17162,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>74</v>
       </c>
@@ -17309,7 +17309,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="73" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>75</v>
       </c>
@@ -17462,7 +17462,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="74" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>76</v>
       </c>
@@ -17703,7 +17703,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="75" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>77</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="76" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>78</v>
       </c>
@@ -18175,7 +18175,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="77" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>79</v>
       </c>
@@ -18318,7 +18318,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="78" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>80</v>
       </c>
@@ -18517,7 +18517,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="79" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>81</v>
       </c>
@@ -18662,7 +18662,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="80" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>82</v>
       </c>
@@ -18901,7 +18901,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="81" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>83</v>
       </c>
@@ -19140,7 +19140,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="82" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>84</v>
       </c>
@@ -19373,7 +19373,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="83" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>85</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="84" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>86</v>
       </c>
@@ -19741,7 +19741,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="85" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>87</v>
       </c>
@@ -19934,7 +19934,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="86" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>88</v>
       </c>
@@ -20073,7 +20073,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="87" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>89</v>
       </c>
@@ -20208,7 +20208,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="88" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>90</v>
       </c>
@@ -20461,7 +20461,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="89" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>91</v>
       </c>
@@ -20596,7 +20596,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="90" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>92</v>
       </c>
@@ -20735,7 +20735,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="91" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>93</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="92" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>94</v>
       </c>
@@ -21061,7 +21061,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="93" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>95</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="94" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>96</v>
       </c>
@@ -21345,7 +21345,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="95" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>97</v>
       </c>
@@ -21484,7 +21484,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="96" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>98</v>
       </c>
@@ -21623,7 +21623,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="97" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>99</v>
       </c>
@@ -21852,7 +21852,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="98" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>100</v>
       </c>
@@ -21991,7 +21991,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="99" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>101</v>
       </c>
@@ -22170,7 +22170,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="100" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>102</v>
       </c>
@@ -22355,7 +22355,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="101" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>103</v>
       </c>
@@ -22534,7 +22534,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="102" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>104</v>
       </c>
@@ -22713,7 +22713,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="103" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>105</v>
       </c>
@@ -22898,7 +22898,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="104" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>106</v>
       </c>
@@ -23037,7 +23037,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="105" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>107</v>
       </c>
@@ -23182,7 +23182,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="106" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>108</v>
       </c>
@@ -23419,7 +23419,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="107" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>109</v>
       </c>
@@ -23656,7 +23656,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="108" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>110</v>
       </c>
@@ -23885,7 +23885,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="109" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>111</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="110" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>112</v>
       </c>
@@ -24207,7 +24207,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="111" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>113</v>
       </c>
@@ -24354,7 +24354,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="112" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>114</v>
       </c>
@@ -24493,7 +24493,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="113" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>115</v>
       </c>
@@ -24632,7 +24632,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="114" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>116</v>
       </c>
@@ -24771,7 +24771,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>117</v>
       </c>
@@ -24918,7 +24918,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="116" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>118</v>
       </c>
@@ -25067,7 +25067,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="117" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>119</v>
       </c>
@@ -25258,7 +25258,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="118" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>120</v>
       </c>
@@ -25445,7 +25445,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="119" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>121</v>
       </c>
@@ -25682,7 +25682,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="120" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>122</v>
       </c>
@@ -25873,7 +25873,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="121" spans="1:87" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:87" ht="30" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>123</v>
       </c>
@@ -26104,7 +26104,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="122" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>124</v>
       </c>
@@ -26335,7 +26335,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="123" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>125</v>
       </c>
@@ -26570,7 +26570,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="124" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>126</v>
       </c>
@@ -26801,7 +26801,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="125" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>127</v>
       </c>
@@ -27032,7 +27032,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="126" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>128</v>
       </c>
@@ -27269,7 +27269,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="127" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>129</v>
       </c>
@@ -27416,7 +27416,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="128" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>130</v>
       </c>
@@ -27599,7 +27599,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="129" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>131</v>
       </c>
@@ -27782,7 +27782,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="130" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>132</v>
       </c>
@@ -28019,7 +28019,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="131" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>133</v>
       </c>
@@ -28202,7 +28202,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="132" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>134</v>
       </c>
@@ -28349,7 +28349,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="133" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>135</v>
       </c>
@@ -28486,7 +28486,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="134" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>136</v>
       </c>
@@ -28725,7 +28725,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="135" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>137</v>
       </c>
@@ -28908,7 +28908,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="136" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>138</v>
       </c>
@@ -29137,7 +29137,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>139</v>
       </c>
@@ -29276,7 +29276,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="138" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>140</v>
       </c>
@@ -29413,7 +29413,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="139" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>141</v>
       </c>
@@ -29550,7 +29550,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="140" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>142</v>
       </c>
@@ -29685,7 +29685,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="141" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>143</v>
       </c>
@@ -29820,7 +29820,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="142" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>144</v>
       </c>
@@ -29959,7 +29959,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="143" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>145</v>
       </c>
@@ -30188,7 +30188,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="144" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>146</v>
       </c>
@@ -30327,7 +30327,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="145" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>147</v>
       </c>
@@ -30556,7 +30556,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="146" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>148</v>
       </c>
@@ -30739,7 +30739,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="147" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>149</v>
       </c>
@@ -30922,7 +30922,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="148" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>150</v>
       </c>
@@ -31061,7 +31061,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="149" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>151</v>
       </c>
@@ -31208,7 +31208,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="150" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>152</v>
       </c>
@@ -31449,7 +31449,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="151" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>153</v>
       </c>
@@ -31688,7 +31688,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="152" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>154</v>
       </c>
@@ -31917,7 +31917,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="153" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>155</v>
       </c>
@@ -32056,7 +32056,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="154" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>156</v>
       </c>
@@ -32203,7 +32203,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="155" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>157</v>
       </c>
@@ -32438,7 +32438,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="156" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>158</v>
       </c>
@@ -32577,7 +32577,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>159</v>
       </c>
@@ -32806,7 +32806,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="158" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>160</v>
       </c>
@@ -33035,7 +33035,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="159" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>161</v>
       </c>
@@ -33272,7 +33272,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="160" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>162</v>
       </c>
@@ -33419,7 +33419,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="161" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>163</v>
       </c>
@@ -33566,7 +33566,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="162" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>164</v>
       </c>
@@ -33799,7 +33799,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="163" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>165</v>
       </c>
@@ -33984,7 +33984,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="164" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>166</v>
       </c>
@@ -34167,7 +34167,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="165" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>167</v>
       </c>
@@ -34306,7 +34306,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="166" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>168</v>
       </c>
@@ -34445,7 +34445,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="167" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>169</v>
       </c>
@@ -34672,7 +34672,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="168" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>170</v>
       </c>
@@ -34875,7 +34875,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="169" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>171</v>
       </c>
@@ -35070,7 +35070,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="170" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>172</v>
       </c>
@@ -35165,7 +35165,7 @@
       <c r="CH170" s="1"/>
       <c r="CI170" s="1"/>
     </row>
-    <row r="171" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>173</v>
       </c>
@@ -35408,7 +35408,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="172" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>174</v>
       </c>
@@ -35547,7 +35547,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="173" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>175</v>
       </c>
@@ -35686,7 +35686,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="174" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>176</v>
       </c>
@@ -35917,7 +35917,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="175" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>177</v>
       </c>
@@ -36146,7 +36146,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="176" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>178</v>
       </c>
@@ -36283,7 +36283,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="177" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>179</v>
       </c>
@@ -36430,7 +36430,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="178" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>180</v>
       </c>
@@ -36665,7 +36665,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="179" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>181</v>
       </c>
@@ -36804,7 +36804,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="180" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>182</v>
       </c>
@@ -36951,7 +36951,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="181" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>183</v>
       </c>
@@ -37094,7 +37094,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="182" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>184</v>
       </c>
@@ -37233,7 +37233,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="183" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>185</v>
       </c>
@@ -37372,7 +37372,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="184" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>186</v>
       </c>
@@ -37551,7 +37551,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="185" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>187</v>
       </c>
@@ -37736,7 +37736,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="186" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>188</v>
       </c>
@@ -37965,7 +37965,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="187" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>189</v>
       </c>
@@ -38150,7 +38150,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="188" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>190</v>
       </c>
@@ -38377,7 +38377,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="189" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>191</v>
       </c>
@@ -38516,7 +38516,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="190" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>192</v>
       </c>
@@ -38745,7 +38745,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="191" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>193</v>
       </c>
@@ -38884,7 +38884,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="192" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>194</v>
       </c>
@@ -39031,7 +39031,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="193" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>195</v>
       </c>
@@ -39214,7 +39214,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="194" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>196</v>
       </c>
@@ -39353,7 +39353,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="195" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>197</v>
       </c>
@@ -39536,7 +39536,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="196" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>198</v>
       </c>
@@ -39785,7 +39785,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="197" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>199</v>
       </c>
@@ -40016,7 +40016,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="198" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>200</v>
       </c>
@@ -40245,7 +40245,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="199" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>201</v>
       </c>
@@ -40430,7 +40430,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="200" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>202</v>
       </c>
@@ -40569,7 +40569,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="201" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>203</v>
       </c>
@@ -40822,7 +40822,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="202" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>204</v>
       </c>
@@ -41017,7 +41017,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="203" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>205</v>
       </c>
@@ -41198,7 +41198,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="204" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>206</v>
       </c>
@@ -41389,7 +41389,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="205" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>207</v>
       </c>
@@ -41626,7 +41626,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="206" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>208</v>
       </c>
@@ -41855,7 +41855,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="207" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>209</v>
       </c>
@@ -42008,7 +42008,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="208" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>210</v>
       </c>
@@ -42161,7 +42161,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="209" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>211</v>
       </c>
@@ -42372,7 +42372,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="210" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>212</v>
       </c>
@@ -42555,7 +42555,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="211" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>213</v>
       </c>
@@ -42740,7 +42740,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="212" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>214</v>
       </c>
@@ -42969,7 +42969,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="213" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>215</v>
       </c>
@@ -43158,7 +43158,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="214" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>216</v>
       </c>
@@ -43297,7 +43297,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="215" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>217</v>
       </c>
@@ -43478,7 +43478,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="216" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>218</v>
       </c>
@@ -43707,7 +43707,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="217" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>219</v>
       </c>
@@ -43856,7 +43856,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="218" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>220</v>
       </c>
@@ -43999,7 +43999,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="219" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>221</v>
       </c>
@@ -44182,7 +44182,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="220" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>222</v>
       </c>
@@ -44367,7 +44367,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="221" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>223</v>
       </c>
@@ -44510,7 +44510,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="222" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>224</v>
       </c>
@@ -44605,7 +44605,7 @@
       <c r="CH222" s="1"/>
       <c r="CI222" s="1"/>
     </row>
-    <row r="223" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>225</v>
       </c>
@@ -44788,7 +44788,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="224" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>226</v>
       </c>
@@ -45037,7 +45037,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="225" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>227</v>
       </c>
@@ -45280,7 +45280,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="226" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>228</v>
       </c>
@@ -45469,7 +45469,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="227" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>229</v>
       </c>
@@ -45608,7 +45608,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="228" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>230</v>
       </c>
@@ -45791,7 +45791,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="229" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>231</v>
       </c>
@@ -45978,7 +45978,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="230" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>232</v>
       </c>
@@ -46117,7 +46117,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="231" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>233</v>
       </c>
@@ -46300,7 +46300,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="232" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>234</v>
       </c>
@@ -46453,7 +46453,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="233" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>235</v>
       </c>
@@ -46636,7 +46636,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="234" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>236</v>
       </c>
@@ -46875,7 +46875,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="235" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>237</v>
       </c>
@@ -47036,7 +47036,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="236" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>238</v>
       </c>
@@ -47265,7 +47265,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="237" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>239</v>
       </c>
@@ -47404,7 +47404,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="238" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>240</v>
       </c>
@@ -47641,7 +47641,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="239" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>241</v>
       </c>
@@ -47878,7 +47878,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="240" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>242</v>
       </c>
@@ -48125,7 +48125,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="241" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>243</v>
       </c>
@@ -48362,7 +48362,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="242" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>244</v>
       </c>
@@ -48591,7 +48591,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="243" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>245</v>
       </c>
@@ -48730,7 +48730,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="244" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>246</v>
       </c>
@@ -48965,7 +48965,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="245" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>247</v>
       </c>
@@ -49112,7 +49112,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="246" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>248</v>
       </c>
@@ -49347,7 +49347,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="247" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>249</v>
       </c>
@@ -49592,7 +49592,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="248" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>250</v>
       </c>
@@ -49731,7 +49731,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="249" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>251</v>
       </c>
@@ -49980,7 +49980,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="250" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>252</v>
       </c>
@@ -50221,7 +50221,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="251" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>253</v>
       </c>
@@ -50374,7 +50374,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="252" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>254</v>
       </c>
@@ -50521,7 +50521,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="253" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>255</v>
       </c>
@@ -50750,7 +50750,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="254" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>256</v>
       </c>
@@ -50979,7 +50979,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="255" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>257</v>
       </c>
@@ -51126,7 +51126,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="256" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>258</v>
       </c>
@@ -51265,7 +51265,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="257" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>259</v>
       </c>
@@ -51410,7 +51410,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="258" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>260</v>
       </c>
@@ -51549,7 +51549,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="259" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>261</v>
       </c>
@@ -51738,7 +51738,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="260" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>262</v>
       </c>
@@ -51979,7 +51979,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="261" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>263</v>
       </c>
@@ -52208,7 +52208,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="262" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>264</v>
       </c>
@@ -52419,7 +52419,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="263" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>265</v>
       </c>
@@ -52558,7 +52558,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="264" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>266</v>
       </c>
@@ -52701,7 +52701,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="265" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>267</v>
       </c>
@@ -52930,7 +52930,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="266" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>268</v>
       </c>
@@ -53171,7 +53171,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="267" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>269</v>
       </c>
@@ -53358,7 +53358,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="268" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>270</v>
       </c>
@@ -53585,7 +53585,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="269" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>271</v>
       </c>
@@ -53770,7 +53770,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="270" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>272</v>
       </c>
@@ -53915,7 +53915,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="271" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>273</v>
       </c>
@@ -54062,7 +54062,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="272" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>274</v>
       </c>
@@ -54305,7 +54305,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="273" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>275</v>
       </c>
@@ -54534,7 +54534,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="274" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>276</v>
       </c>
@@ -54717,7 +54717,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="275" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>277</v>
       </c>
@@ -54942,7 +54942,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="276" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>278</v>
       </c>
@@ -55089,7 +55089,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="277" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>279</v>
       </c>
@@ -55314,7 +55314,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="278" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>280</v>
       </c>
@@ -55539,7 +55539,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="279" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>281</v>
       </c>
@@ -55684,7 +55684,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="280" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>282</v>
       </c>
@@ -55869,7 +55869,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="281" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>283</v>
       </c>
@@ -56098,7 +56098,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="282" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>284</v>
       </c>
@@ -56235,7 +56235,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="283" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>285</v>
       </c>
@@ -56418,7 +56418,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="284" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>286</v>
       </c>
@@ -56609,7 +56609,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="285" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>287</v>
       </c>
@@ -56746,7 +56746,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="286" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>288</v>
       </c>
@@ -56975,7 +56975,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="287" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>289</v>
       </c>
@@ -57166,7 +57166,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="288" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>290</v>
       </c>
@@ -57319,7 +57319,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="289" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>291</v>
       </c>
@@ -57544,7 +57544,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="290" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>292</v>
       </c>
@@ -57769,7 +57769,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="291" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>293</v>
       </c>
@@ -57908,7 +57908,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="292" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>294</v>
       </c>
@@ -58047,7 +58047,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="293" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>295</v>
       </c>
@@ -58296,7 +58296,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="294" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>296</v>
       </c>
@@ -58435,7 +58435,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="295" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>297</v>
       </c>
@@ -58622,7 +58622,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="296" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>298</v>
       </c>
@@ -58859,7 +58859,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="297" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>299</v>
       </c>
@@ -59042,7 +59042,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="298" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>300</v>
       </c>
@@ -59271,7 +59271,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="299" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>301</v>
       </c>
@@ -59418,7 +59418,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="300" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>302</v>
       </c>
@@ -59649,7 +59649,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="301" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>303</v>
       </c>
@@ -59838,7 +59838,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="302" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>304</v>
       </c>
@@ -60075,7 +60075,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="303" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>305</v>
       </c>
@@ -60304,7 +60304,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="304" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>306</v>
       </c>
@@ -60451,7 +60451,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="305" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>307</v>
       </c>
@@ -60634,7 +60634,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="306" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>308</v>
       </c>
@@ -60813,7 +60813,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="307" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>309</v>
       </c>
@@ -61064,7 +61064,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="308" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>310</v>
       </c>
@@ -61207,7 +61207,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="309" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>311</v>
       </c>
@@ -61398,7 +61398,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="310" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>312</v>
       </c>
@@ -61537,7 +61537,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="311" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>313</v>
       </c>
@@ -61632,7 +61632,7 @@
       <c r="CH311" s="1"/>
       <c r="CI311" s="1"/>
     </row>
-    <row r="312" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>314</v>
       </c>
@@ -61771,7 +61771,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="313" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>315</v>
       </c>
@@ -61954,7 +61954,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="314" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>316</v>
       </c>
@@ -62093,7 +62093,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="315" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>317</v>
       </c>
@@ -62240,7 +62240,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="316" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>318</v>
       </c>
@@ -62469,7 +62469,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="317" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>319</v>
       </c>
@@ -62728,7 +62728,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="318" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>320</v>
       </c>
@@ -62875,7 +62875,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="319" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>321</v>
       </c>
@@ -63014,7 +63014,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="320" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>322</v>
       </c>
@@ -63173,7 +63173,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="321" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>323</v>
       </c>
@@ -63376,7 +63376,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="322" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>324</v>
       </c>
@@ -63613,7 +63613,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="323" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>325</v>
       </c>
@@ -63800,7 +63800,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="324" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>326</v>
       </c>
@@ -64037,7 +64037,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="325" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>327</v>
       </c>
@@ -64266,7 +64266,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="326" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>328</v>
       </c>
@@ -64495,7 +64495,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="327" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>329</v>
       </c>
@@ -64748,7 +64748,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="328" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>330</v>
       </c>
@@ -64895,7 +64895,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="329" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>331</v>
       </c>
@@ -65042,7 +65042,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="330" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>332</v>
       </c>
@@ -65229,7 +65229,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="331" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>333</v>
       </c>
@@ -65376,7 +65376,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="332" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>334</v>
       </c>
@@ -65529,7 +65529,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="333" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>335</v>
       </c>
@@ -65766,7 +65766,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="334" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>336</v>
       </c>
@@ -66001,7 +66001,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="335" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>337</v>
       </c>
@@ -66248,7 +66248,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="336" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>338</v>
       </c>
@@ -66477,7 +66477,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="337" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>339</v>
       </c>
@@ -66670,7 +66670,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="338" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>340</v>
       </c>
@@ -66907,7 +66907,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="339" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>341</v>
       </c>
@@ -67052,7 +67052,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="340" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>342</v>
       </c>
@@ -67247,7 +67247,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="341" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>343</v>
       </c>
@@ -67394,7 +67394,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="342" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>344</v>
       </c>
@@ -67541,7 +67541,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="343" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>345</v>
       </c>
@@ -67772,7 +67772,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="344" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>346</v>
       </c>
@@ -67965,7 +67965,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="345" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>347</v>
       </c>
@@ -68166,7 +68166,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="346" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>348</v>
       </c>
@@ -68305,7 +68305,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="347" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>349</v>
       </c>
@@ -68496,7 +68496,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="348" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>350</v>
       </c>
@@ -68733,7 +68733,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="349" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>351</v>
       </c>
@@ -68962,7 +68962,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="350" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>352</v>
       </c>
@@ -69155,7 +69155,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="351" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>353</v>
       </c>
@@ -69390,7 +69390,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="352" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>354</v>
       </c>
@@ -69619,7 +69619,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="353" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>355</v>
       </c>
@@ -69874,7 +69874,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="354" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>356</v>
       </c>
@@ -70103,7 +70103,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="355" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>357</v>
       </c>
@@ -70288,7 +70288,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="356" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>358</v>
       </c>
@@ -70469,7 +70469,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="357" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>359</v>
       </c>
@@ -70616,7 +70616,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="358" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>360</v>
       </c>
@@ -70755,7 +70755,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="359" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>361</v>
       </c>
@@ -70890,7 +70890,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="360" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>362</v>
       </c>
@@ -71035,7 +71035,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="361" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>363</v>
       </c>
@@ -71174,7 +71174,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="362" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>364</v>
       </c>
@@ -71355,7 +71355,7 @@
         <v>19</v>
       </c>
       <c r="CF362" s="4" t="s">
-        <v>1126</v>
+        <v>1059</v>
       </c>
       <c r="CG362" s="1" t="s">
         <v>30</v>
@@ -71367,7 +71367,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="363" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>365</v>
       </c>
@@ -71596,7 +71596,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="364" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>366</v>
       </c>
@@ -71789,7 +71789,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="365" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>367</v>
       </c>
@@ -71936,7 +71936,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="366" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>368</v>
       </c>
@@ -72167,7 +72167,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="367" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>369</v>
       </c>
@@ -72306,7 +72306,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="368" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>370</v>
       </c>
@@ -72511,7 +72511,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="369" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>371</v>
       </c>
@@ -72742,7 +72742,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="370" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>372</v>
       </c>
@@ -72881,7 +72881,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="371" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>373</v>
       </c>
@@ -73120,7 +73120,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="372" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>374</v>
       </c>
@@ -73267,7 +73267,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="373" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>375</v>
       </c>
@@ -73412,7 +73412,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="374" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>376</v>
       </c>
@@ -73645,7 +73645,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="375" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>377</v>
       </c>
@@ -73874,7 +73874,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="376" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>378</v>
       </c>
@@ -74103,7 +74103,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="377" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>379</v>
       </c>
@@ -74238,7 +74238,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="378" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>380</v>
       </c>
@@ -74377,7 +74377,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="379" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>381</v>
       </c>
@@ -74514,7 +74514,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="380" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>382</v>
       </c>
@@ -74751,7 +74751,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="381" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>383</v>
       </c>
@@ -74982,7 +74982,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="382" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>384</v>
       </c>
@@ -75217,7 +75217,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="383" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>385</v>
       </c>
@@ -75360,7 +75360,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="384" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>386</v>
       </c>
